--- a/Sufficient data WITH_PO/forecast_summary_B0DJP9LCYC_WITH_PO.xlsx
+++ b/Sufficient data WITH_PO/forecast_summary_B0DJP9LCYC_WITH_PO.xlsx
@@ -487,12 +487,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12.17</v>
+        <v>11.79</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -529,11 +529,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.9</v>
+        <v>1.13</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -544,12 +544,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10.56</v>
+        <v>10.79</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -601,12 +601,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10.63</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -643,11 +643,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.95</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -658,12 +658,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -700,11 +700,11 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -715,12 +715,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9.1</v>
+        <v>9.66</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -757,11 +757,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W29</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8.1</v>
+        <v>6.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -814,11 +814,11 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -829,12 +829,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>W32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7.91</v>
+        <v>5.66</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -886,12 +886,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.2</v>
+        <v>4.66</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -928,11 +928,11 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.9</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -943,12 +943,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -985,11 +985,11 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1000,12 +1000,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.68</v>
+        <v>2.9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1042,11 +1042,11 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1057,12 +1057,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.68</v>
+        <v>1.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1114,12 +1114,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.68</v>
+        <v>0.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1151,16 +1151,16 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Urgent</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1171,12 +1171,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W36</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1199,25 +1199,25 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Urgent</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W37</t>
+          <t>W39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1270,11 +1270,11 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1285,12 +1285,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W38</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1327,11 +1327,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W39</t>
+          <t>W41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1384,11 +1384,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Increasing (▲)</t>
+          <t>Decreasing (▼)</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-10-06 to 2025-06-01</t>
+          <t>2024-10-06 to 2025-06-15</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>125 units</t>
+          <t>129 units</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
